--- a/data/trending_integrated_20261020_14.xlsx
+++ b/data/trending_integrated_20261020_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72600</v>
+        <v>73400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.56%</t>
+          <t>'+13.80%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>140073430400</v>
+        <v>142489632550</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3235</v>
+        <v>3180</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.98%</t>
+          <t>'+9.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>50362327974</v>
+        <v>52579696317</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 사망설 루머 확산에 따른 급등. 과거 유사 사례 재현 기대감 형성.</t>
+          <t xml:space="preserve">김정은 사망설 관련 루머로 급등. 과거 사례 언급하며 기대감 표출. 불확실성으로 인한 변동성. </t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '루머', '급등']</t>
+          <t>['김정은', '사망설', '루머']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10010</v>
+        <v>9800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.76%</t>
+          <t>'+7.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G4" t="n">
-        <v>492</v>
+        <v>532</v>
       </c>
       <c r="H4" t="n">
         <v>0.88</v>
@@ -794,7 +794,7 @@
         <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>229573165650</v>
+        <v>236743005470</v>
       </c>
       <c r="P4" t="n">
         <v>11250</v>
@@ -810,12 +810,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 등 다양한 섹터 연관성 부각. 조단위 시총 기대감 형성 및 신고가 경신.</t>
+          <t>로봇, ESS, 이차전지 관련주로 언급. 주포의 의지와 임원 매수 언급. 투경 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3950</v>
+        <v>3975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.33%</t>
+          <t>'+6.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
         <v>1.66</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>45207835254</v>
+        <v>46583395254</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16150</v>
+        <v>42900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.31%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>244</v>
+        <v>1143</v>
       </c>
       <c r="H6" t="n">
-        <v>2.03</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16200</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>16500</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>18620</v>
+        <v>43200</v>
       </c>
       <c r="M6" t="n">
-        <v>14650</v>
+        <v>41550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>59879850975</v>
+        <v>14194030350</v>
       </c>
       <c r="P6" t="n">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>14600</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-52000</v>
+        <v>-20000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개잡주, 쓰레기 종목 비난. 보호예수 물량 출회 및 주가 하락 우려.</t>
+          <t>C1 발표 및 담관암 FDA 승인 관련 기대감 존재. 일부 부정적 전망도 있으나 전반적 긍정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['개잡주', '보호예수', '주가 하락']</t>
+          <t>['C1', 'FDA', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42700</v>
+        <v>16065</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E7" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F7" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>1047</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K7" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L7" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M7" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N7" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>13793952550</v>
+        <v>61280034245</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R7" t="n">
-        <v>-20000</v>
+        <v>-52000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB의 C1 발표 및 담관암 FDA 승인 가능성에 대한 기대감. 클래스 1 확신 및 100만원 목표가 제시.</t>
+          <t>보호예수 물량 출회 우려 및 개잡주 평가. 빅웨이브와 비교하며 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1발표', 'FDA승인', '담관암']</t>
+          <t>['보호예수', '개잡주', '물량']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>10619152395</v>
+        <v>10885551525</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210000</v>
+        <v>211750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G9" t="n">
-        <v>1472</v>
+        <v>1548</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2237184005250</v>
+        <v>2340273360750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 발언 다수. 증시 부진에 대한 정부 정책 비판.</t>
+          <t>정치적 이슈와 맞물려 급락세. 연기금 매도 및 정부 정책 불신 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '증시 부진', '정책 비판']</t>
+          <t>['정치', '증시', '정책']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18740</v>
+        <v>1221000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-4.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.25</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>577</v>
       </c>
       <c r="G10" t="n">
-        <v>175</v>
+        <v>1753</v>
       </c>
       <c r="H10" t="n">
-        <v>3.07</v>
+        <v>48.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19710</v>
+        <v>1277000</v>
       </c>
       <c r="K10" t="n">
-        <v>19450</v>
+        <v>1265000</v>
       </c>
       <c r="L10" t="n">
-        <v>21850</v>
+        <v>1267000</v>
       </c>
       <c r="M10" t="n">
-        <v>18460</v>
+        <v>1183000</v>
       </c>
       <c r="N10" t="n">
-        <v>3.32</v>
+        <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>96755750235</v>
+        <v>3166045620500</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>465500</v>
       </c>
       <c r="R10" t="n">
-        <v>-20000</v>
+        <v>-270000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-186000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>라온시큐어 보안주로서의 중요성 부각 및 주가 상승 기대. 2만원 안착 여부 및 외국인 매수세 주목.</t>
+          <t>솔리다임 우회상장 반대 청원 및 경영진 비판. 정치적 이슈와 겹쳐 급락.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', '정책', '외국인']</t>
+          <t>['솔리다임', '우회상장', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1214000</v>
+        <v>18800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-4.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
-        <v>572</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>1786</v>
+        <v>176</v>
       </c>
       <c r="H11" t="n">
-        <v>48.81</v>
+        <v>3.07</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1277000</v>
+        <v>19710</v>
       </c>
       <c r="K11" t="n">
-        <v>1265000</v>
+        <v>19450</v>
       </c>
       <c r="L11" t="n">
-        <v>1267000</v>
+        <v>21850</v>
       </c>
       <c r="M11" t="n">
-        <v>1183000</v>
+        <v>18460</v>
       </c>
       <c r="N11" t="n">
-        <v>48.82</v>
+        <v>3.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3073628862000</v>
+        <v>97814056350</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>465500</v>
+        <v>6320</v>
       </c>
       <c r="R11" t="n">
-        <v>-270000</v>
+        <v>-20000</v>
       </c>
       <c r="S11" t="n">
-        <v>-186000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>솔리다임 우회 상장 논란 및 최태원 회장 관련 비판. 소액주주 보호 청원 제기.</t>
+          <t>라온시큐어 보안주로서의 중요성 부각 및 주가 상승 기대. 2만원 안착 여부 및 외국인 매수세 주목.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회 상장', '소액주주']</t>
+          <t>['보안주', '정책', '외국인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14190</v>
+        <v>14240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.08%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H12" t="n">
         <v>9.779999999999999</v>
@@ -1524,13 +1524,13 @@
         <v>14940</v>
       </c>
       <c r="M12" t="n">
-        <v>14150</v>
+        <v>14110</v>
       </c>
       <c r="N12" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>20024947030</v>
+        <v>21268034835</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17310</v>
+        <v>17410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.41%</t>
+          <t>'-4.86%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="H13" t="n">
         <v>27.78</v>
@@ -1622,7 +1622,7 @@
         <v>27.85</v>
       </c>
       <c r="O13" t="n">
-        <v>39492750980</v>
+        <v>40839389800</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2530</v>
+        <v>2545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.12%</t>
+          <t>'-5.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>30546386119</v>
+        <v>30770387850</v>
       </c>
       <c r="P14" t="n">
         <v>2755</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30750</v>
+        <v>30950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.43%</t>
+          <t>'-8.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>62953473575</v>
+        <v>64503015225</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.95%</t>
+          <t>'-9.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F16" t="n">
         <v>102</v>
       </c>
       <c r="G16" t="n">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1892,13 +1892,13 @@
         <v>1895</v>
       </c>
       <c r="M16" t="n">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="N16" t="n">
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>71448035677</v>
+        <v>71842263976</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시와 함께 급등세 연출. 글로벌 강관 기술력 입증 및 우주사업 기대감 형성.</t>
+          <t>스페이스X 납품 관련 호재 공시로 급등세. 2연상 기대감 존재. 외인 비중 소폭 증가.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '글로벌 강관']</t>
+          <t>['스페이스X', '철강', '납품']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8670</v>
+        <v>8700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-10.80%</t>
+          <t>'-10.49%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17431456785</v>
+        <v>17513160430</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>테슬라 부품 공급 및 주주환원 정책 부재에 대한 불만. 중복 상장 우려 제기.</t>
+          <t>테슬라 부품 공급 관련 언급. 주주환원 부재 및 과거 주가 흐름에 대한 부정적 시각 존재. 급락.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['테슬라', '주주환원', '중복 상장']</t>
+          <t>['테슬라', '부품', '주주환원']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>70800</v>
+        <v>7740</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.66%</t>
+          <t>'-13.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="F18" t="n">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>833</v>
+        <v>171</v>
       </c>
       <c r="H18" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L18" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M18" t="n">
-        <v>70300</v>
+        <v>7600</v>
       </c>
       <c r="N18" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>108529824500</v>
+        <v>20127199195</v>
       </c>
       <c r="P18" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q18" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R18" t="n">
-        <v>-557000</v>
+        <v>-72000</v>
       </c>
       <c r="S18" t="n">
-        <v>-77000</v>
+        <v>-33000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>한화시스템 주가 급락에 대한 공매도 및 정부 정책 비판. 이유 없는 하락에 대한 불만 제기.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '정부정책', '주가하락']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,91 +2115,91 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7670</v>
+        <v>70600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-14.21%</t>
+          <t>'-13.90%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="G19" t="n">
-        <v>167</v>
+        <v>862</v>
       </c>
       <c r="H19" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K19" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L19" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M19" t="n">
-        <v>7640</v>
+        <v>70000</v>
       </c>
       <c r="N19" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>19646529695</v>
+        <v>112190921950</v>
       </c>
       <c r="P19" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q19" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R19" t="n">
-        <v>-72000</v>
+        <v>-557000</v>
       </c>
       <c r="S19" t="n">
-        <v>-33000</v>
+        <v>-77000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '정치', '급락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_14.xlsx
+++ b/data/trending_integrated_20261020_14.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73400</v>
+        <v>3325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+13.80%</t>
+          <t>'+14.07%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="H2" t="n">
-        <v>5.95</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>64500</v>
+        <v>2915</v>
       </c>
       <c r="K2" t="n">
-        <v>68000</v>
+        <v>2920</v>
       </c>
       <c r="L2" t="n">
-        <v>79300</v>
+        <v>3445</v>
       </c>
       <c r="M2" t="n">
-        <v>66700</v>
+        <v>2875</v>
       </c>
       <c r="N2" t="n">
-        <v>5.66</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>142489632550</v>
+        <v>55259600717</v>
       </c>
       <c r="P2" t="n">
-        <v>148300</v>
+        <v>7050</v>
       </c>
       <c r="Q2" t="n">
-        <v>17780</v>
+        <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>-1000</v>
+        <v>-831000</v>
       </c>
       <c r="S2" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
+          <t>김정은 사망설 관련 지정학적 리스크 부각으로 인한 급등 가능성 언급. 과거 유사 사례 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '실적', '목표가']</t>
+          <t>['김정은 사망설', '지정학적 리스크', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,91 +643,91 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3180</v>
+        <v>72900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.09%</t>
+          <t>'+13.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.73</v>
+        <v>5.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2915</v>
+        <v>64500</v>
       </c>
       <c r="K3" t="n">
-        <v>2920</v>
+        <v>68000</v>
       </c>
       <c r="L3" t="n">
-        <v>3445</v>
+        <v>79300</v>
       </c>
       <c r="M3" t="n">
-        <v>2875</v>
+        <v>66700</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>5.66</v>
       </c>
       <c r="O3" t="n">
-        <v>52579696317</v>
+        <v>144468859150</v>
       </c>
       <c r="P3" t="n">
-        <v>7050</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2500</v>
+        <v>17780</v>
       </c>
       <c r="R3" t="n">
-        <v>-678000</v>
+        <v>-17000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">김정은 사망설 관련 루머로 급등. 과거 사례 언급하며 기대감 표출. 불확실성으로 인한 변동성. </t>
+          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은', '사망설', '루머']</t>
+          <t>['반도체', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9800</v>
+        <v>4030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.46%</t>
+          <t>'+7.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>224</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>532</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>1.66</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9120</v>
+        <v>3750</v>
       </c>
       <c r="K4" t="n">
-        <v>9500</v>
+        <v>3770</v>
       </c>
       <c r="L4" t="n">
-        <v>11250</v>
+        <v>4285</v>
       </c>
       <c r="M4" t="n">
-        <v>9470</v>
+        <v>3755</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>236743005470</v>
+        <v>47215472686</v>
       </c>
       <c r="P4" t="n">
-        <v>11250</v>
+        <v>6660</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>2200</v>
       </c>
       <c r="R4" t="n">
-        <v>259000</v>
+        <v>-138000</v>
       </c>
       <c r="S4" t="n">
-        <v>25000</v>
+        <v>-18000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 관련주로 언급. 주포의 의지와 임원 매수 언급. 투경 우려.</t>
+          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '이차전지']</t>
+          <t>['피하주사', '기술 계약', '시장 하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3975</v>
+        <v>9630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.00%</t>
+          <t>'+5.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>564</v>
       </c>
       <c r="H5" t="n">
-        <v>1.66</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3750</v>
+        <v>9120</v>
       </c>
       <c r="K5" t="n">
-        <v>3770</v>
+        <v>9500</v>
       </c>
       <c r="L5" t="n">
-        <v>4285</v>
+        <v>11250</v>
       </c>
       <c r="M5" t="n">
-        <v>3755</v>
+        <v>9470</v>
       </c>
       <c r="N5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>46583395254</v>
+        <v>240032798925</v>
       </c>
       <c r="P5" t="n">
-        <v>6660</v>
+        <v>11250</v>
       </c>
       <c r="Q5" t="n">
-        <v>2200</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>-136000</v>
+        <v>76000</v>
       </c>
       <c r="S5" t="n">
-        <v>-18000</v>
+        <v>22000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
+          <t>로봇, ESS, 이차전지 관련 복합적인 사업 포트폴리오 보유 및 신고가 돌파 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['피하주사', '기술 계약', '시장 하락']</t>
+          <t>['로봇', 'ESS', '이차전지']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42900</v>
+        <v>16190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="F6" t="n">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>1143</v>
+        <v>271</v>
       </c>
       <c r="H6" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K6" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L6" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M6" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>14194030350</v>
+        <v>61946399275</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R6" t="n">
-        <v>-20000</v>
+        <v>-69000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 및 담관암 FDA 승인 관련 기대감 존재. 일부 부정적 전망도 있으나 전반적 긍정.</t>
+          <t>보호예수 해제 물량 부담 및 실적 불확실성으로 인한 개잡주 의견. 포스코 관련주 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1', 'FDA', '담관암']</t>
+          <t>['보호예수', '실적 불확실', '개잡주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16065</v>
+        <v>42700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
-        <v>250</v>
+        <v>1162</v>
       </c>
       <c r="H7" t="n">
-        <v>2.03</v>
+        <v>13.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16200</v>
+        <v>42950</v>
       </c>
       <c r="K7" t="n">
-        <v>16500</v>
+        <v>42600</v>
       </c>
       <c r="L7" t="n">
-        <v>18620</v>
+        <v>43200</v>
       </c>
       <c r="M7" t="n">
-        <v>14650</v>
+        <v>41550</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07</v>
+        <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>61280034245</v>
+        <v>14391524500</v>
       </c>
       <c r="P7" t="n">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>14600</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>-52000</v>
+        <v>25000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 우려 및 개잡주 평가. 빅웨이브와 비교하며 부정적 전망.</t>
+          <t>C1 발표 임박 및 담관암 FDA 승인 가능성으로 인한 기대감. 주가 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보호예수', '개잡주', '물량']</t>
+          <t>['C1 발표', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>10885551525</v>
+        <v>10985034140</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1171,10 +1171,10 @@
         <v>7190</v>
       </c>
       <c r="R8" t="n">
-        <v>-234000</v>
+        <v>-269000</v>
       </c>
       <c r="S8" t="n">
-        <v>-44000</v>
+        <v>-47000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211750</v>
+        <v>209500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-3.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G9" t="n">
-        <v>1548</v>
+        <v>1498</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2340273360750</v>
+        <v>2431811461750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,14 +1263,14 @@
         <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>858000</v>
+        <v>928000</v>
       </c>
       <c r="S9" t="n">
-        <v>-851000</v>
+        <v>-1301000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 급락세. 연기금 매도 및 정부 정책 불신 표출.</t>
+          <t>현 정부의 증시 정책 부재 및 경제 상황에 대한 부정적 인식과 정치적 이슈로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '증시', '정책']</t>
+          <t>['정치적 이슈', '증시 정책', '경제 상황']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1221000</v>
+        <v>17340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-5.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>577</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>1753</v>
+        <v>271</v>
       </c>
       <c r="H10" t="n">
-        <v>48.81</v>
+        <v>27.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,130 +1331,130 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1277000</v>
+        <v>18300</v>
       </c>
       <c r="K10" t="n">
-        <v>1265000</v>
+        <v>18140</v>
       </c>
       <c r="L10" t="n">
-        <v>1267000</v>
+        <v>18140</v>
       </c>
       <c r="M10" t="n">
-        <v>1183000</v>
+        <v>17280</v>
       </c>
       <c r="N10" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3166045620500</v>
+        <v>41682104555</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-270000</v>
+        <v>-285000</v>
       </c>
       <c r="S10" t="n">
-        <v>-186000</v>
+        <v>-201000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 우회상장 반대 청원 및 경영진 비판. 정치적 이슈와 겹쳐 급락.</t>
+          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '반도체']</t>
+          <t>['조선업', '정부정책', '수주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18800</v>
+        <v>14160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-5.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.25</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="H11" t="n">
-        <v>3.07</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19710</v>
+        <v>14950</v>
       </c>
       <c r="K11" t="n">
-        <v>19450</v>
+        <v>14610</v>
       </c>
       <c r="L11" t="n">
-        <v>21850</v>
+        <v>14940</v>
       </c>
       <c r="M11" t="n">
-        <v>18460</v>
+        <v>14110</v>
       </c>
       <c r="N11" t="n">
-        <v>3.32</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>97814056350</v>
+        <v>21656352175</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-20000</v>
+        <v>-106000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-57000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>라온시큐어 보안주로서의 중요성 부각 및 주가 상승 기대. 2만원 안착 여부 및 외국인 매수세 주목.</t>
+          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안주', '정책', '외국인']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14240</v>
+        <v>1209000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-5.32%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>98</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>581</v>
       </c>
       <c r="G12" t="n">
-        <v>179</v>
+        <v>1827</v>
       </c>
       <c r="H12" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14950</v>
+        <v>1277000</v>
       </c>
       <c r="K12" t="n">
-        <v>14610</v>
+        <v>1265000</v>
       </c>
       <c r="L12" t="n">
-        <v>14940</v>
+        <v>1267000</v>
       </c>
       <c r="M12" t="n">
-        <v>14110</v>
+        <v>1183000</v>
       </c>
       <c r="N12" t="n">
-        <v>9.699999999999999</v>
+        <v>48.82</v>
       </c>
       <c r="O12" t="n">
-        <v>21268034835</v>
+        <v>3234813156000</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>465500</v>
       </c>
       <c r="R12" t="n">
-        <v>-89000</v>
+        <v>-293000</v>
       </c>
       <c r="S12" t="n">
-        <v>-44000</v>
+        <v>-218000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
+          <t>솔리다임 우회 상장 관련 소액주주 보호 청원 및 정치적 이슈로 인한 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['솔리다임', '우회 상장', '소액주주 보호']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,82 +1563,82 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17410</v>
+        <v>18630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-5.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="H13" t="n">
-        <v>27.78</v>
+        <v>3.07</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18300</v>
+        <v>19710</v>
       </c>
       <c r="K13" t="n">
-        <v>18140</v>
+        <v>19450</v>
       </c>
       <c r="L13" t="n">
-        <v>18140</v>
+        <v>21850</v>
       </c>
       <c r="M13" t="n">
-        <v>17280</v>
+        <v>18460</v>
       </c>
       <c r="N13" t="n">
-        <v>27.85</v>
+        <v>3.32</v>
       </c>
       <c r="O13" t="n">
-        <v>40839389800</v>
+        <v>98476846635</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q13" t="n">
-        <v>17210</v>
+        <v>6320</v>
       </c>
       <c r="R13" t="n">
-        <v>-270000</v>
+        <v>19000</v>
       </c>
       <c r="S13" t="n">
-        <v>-171000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
+          <t>라온시큐어 보안주로서의 중요성 부각 및 주가 상승 기대. 2만원 안착 여부 및 외국인 매수세 주목.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선업', '정부정책', '수주']</t>
+          <t>['보안주', '정책', '외국인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2545</v>
+        <v>2535</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.57%</t>
+          <t>'-5.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>30770387850</v>
+        <v>30896710895</v>
       </c>
       <c r="P14" t="n">
         <v>2755</v>
@@ -1723,7 +1723,7 @@
         <v>865</v>
       </c>
       <c r="R14" t="n">
-        <v>57000</v>
+        <v>51000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30950</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.84%</t>
+          <t>'-9.43%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>64503015225</v>
+        <v>65431251775</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1815,10 +1815,10 @@
         <v>22000</v>
       </c>
       <c r="R15" t="n">
-        <v>-365000</v>
+        <v>-430000</v>
       </c>
       <c r="S15" t="n">
-        <v>-64000</v>
+        <v>-82000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.78%</t>
+          <t>'-10.58%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F16" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G16" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>71842263976</v>
+        <v>72061436117</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1907,23 +1907,23 @@
         <v>890</v>
       </c>
       <c r="R16" t="n">
-        <v>-872000</v>
+        <v>-798000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 납품 관련 호재 공시로 급등세. 2연상 기대감 존재. 외인 비중 소폭 증가.</t>
+          <t>스페이스X 관련 호재 공시 및 글로벌 강관 기술력 입증으로 인한 주가 상승 기대. 최근 3일간 코스피 수익률 3위 기록.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '철강', '납품']</t>
+          <t>['스페이스X', '호재 공시', '강관 기술']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8700</v>
+        <v>8640</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-10.49%</t>
+          <t>'-11.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17513160430</v>
+        <v>17621996045</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -1999,10 +1999,10 @@
         <v>5390</v>
       </c>
       <c r="R17" t="n">
-        <v>-187000</v>
+        <v>-181000</v>
       </c>
       <c r="S17" t="n">
-        <v>-530000</v>
+        <v>-535000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7740</v>
+        <v>7680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.42%</t>
+          <t>'-14.09%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H18" t="n">
         <v>36.01</v>
@@ -2082,7 +2082,7 @@
         <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>20127199195</v>
+        <v>20477596835</v>
       </c>
       <c r="P18" t="n">
         <v>19150</v>
@@ -2091,10 +2091,10 @@
         <v>3570</v>
       </c>
       <c r="R18" t="n">
-        <v>-72000</v>
+        <v>-86000</v>
       </c>
       <c r="S18" t="n">
-        <v>-33000</v>
+        <v>-48000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70600</v>
+        <v>70100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.90%</t>
+          <t>'-14.51%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F19" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G19" t="n">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="H19" t="n">
         <v>9.380000000000001</v>
@@ -2174,7 +2174,7 @@
         <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>112190921950</v>
+        <v>114862112850</v>
       </c>
       <c r="P19" t="n">
         <v>184000</v>
@@ -2183,10 +2183,10 @@
         <v>44750</v>
       </c>
       <c r="R19" t="n">
-        <v>-557000</v>
+        <v>-628000</v>
       </c>
       <c r="S19" t="n">
-        <v>-77000</v>
+        <v>-70000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261020_14.xlsx
+++ b/data/trending_integrated_20261020_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3325</v>
+        <v>3290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.07%</t>
+          <t>'+12.86%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>55259600717</v>
+        <v>60925313431</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 지정학적 리스크 부각으로 인한 급등 가능성 언급. 과거 유사 사례 언급.</t>
+          <t>김정은 사망설 루머에 따른 급등 가능성 및 지정학적 리스크 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '지정학적 리스크', '급등']</t>
+          <t>['김정은 사망설', '지정학적 리스크', '급등 가능성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72900</v>
+        <v>72700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.02%</t>
+          <t>'+12.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H3" t="n">
         <v>5.95</v>
@@ -702,7 +702,7 @@
         <v>5.66</v>
       </c>
       <c r="O3" t="n">
-        <v>144468859150</v>
+        <v>145551797850</v>
       </c>
       <c r="P3" t="n">
         <v>148300</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4030</v>
+        <v>3980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.47%</t>
+          <t>'+6.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
         <v>28</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>47215472686</v>
+        <v>47543559896</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9630</v>
+        <v>9470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.59%</t>
+          <t>'+3.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.86</v>
       </c>
       <c r="E5" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F5" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G5" t="n">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -880,13 +880,13 @@
         <v>11250</v>
       </c>
       <c r="M5" t="n">
-        <v>9470</v>
+        <v>9430</v>
       </c>
       <c r="N5" t="n">
         <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>240032798925</v>
+        <v>245116695075</v>
       </c>
       <c r="P5" t="n">
         <v>11250</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 관련 복합적인 사업 포트폴리오 보유 및 신고가 돌파 기대감.</t>
+          <t>로봇, ESS, 이차전지 관련주로서 강한 상승세 및 조단위 시총 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16190</v>
+        <v>42850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>271</v>
+        <v>1173</v>
       </c>
       <c r="H6" t="n">
-        <v>2.03</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16200</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>16500</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>18620</v>
+        <v>43200</v>
       </c>
       <c r="M6" t="n">
-        <v>14650</v>
+        <v>41550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>61946399275</v>
+        <v>14703535950</v>
       </c>
       <c r="P6" t="n">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>14600</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-69000</v>
+        <v>25000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 부담 및 실적 불확실성으로 인한 개잡주 의견. 포스코 관련주 언급.</t>
+          <t>C1 발표 임박 및 담관암 FDA 승인 가능성으로 인한 기대감. 주가 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보호예수', '실적 불확실', '개잡주']</t>
+          <t>['C1 발표', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42700</v>
+        <v>16100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E7" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>1162</v>
+        <v>277</v>
       </c>
       <c r="H7" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K7" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L7" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M7" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N7" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>14391524500</v>
+        <v>62344373440</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R7" t="n">
-        <v>25000</v>
+        <v>-69000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C1 발표 임박 및 담관암 FDA 승인 가능성으로 인한 기대감. 주가 변동성에 대한 언급.</t>
+          <t>종목 부실 및 낮은 상승률에 대한 불만 표출과 보호예수 물량 부담 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '담관암']</t>
+          <t>['부실 종목', '보호예수', '낮은 상승률']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7260</v>
+        <v>7250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
         <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>10985034140</v>
+        <v>11263553950</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209500</v>
+        <v>209750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.90%</t>
+          <t>'-3.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="G9" t="n">
-        <v>1498</v>
+        <v>1538</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2431811461750</v>
+        <v>2513024147750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>현 정부의 증시 정책 부재 및 경제 상황에 대한 부정적 인식과 정치적 이슈로 인한 하락 우려.</t>
+          <t>정치적 이슈에 대한 부정적 언급 및 증시 하락에 대한 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '증시 정책', '경제 상황']</t>
+          <t>['이재명', '정치적 이슈', '증시 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17340</v>
+        <v>1214000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.25%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>574</v>
       </c>
       <c r="G10" t="n">
-        <v>271</v>
+        <v>1927</v>
       </c>
       <c r="H10" t="n">
-        <v>27.78</v>
+        <v>48.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18300</v>
+        <v>1277000</v>
       </c>
       <c r="K10" t="n">
-        <v>18140</v>
+        <v>1265000</v>
       </c>
       <c r="L10" t="n">
-        <v>18140</v>
+        <v>1267000</v>
       </c>
       <c r="M10" t="n">
-        <v>17280</v>
+        <v>1183000</v>
       </c>
       <c r="N10" t="n">
-        <v>27.85</v>
+        <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>41682104555</v>
+        <v>3297565591000</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>465500</v>
       </c>
       <c r="R10" t="n">
-        <v>-285000</v>
+        <v>-293000</v>
       </c>
       <c r="S10" t="n">
-        <v>-201000</v>
+        <v>-218000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
+          <t>솔리다임 중복 상장에 대한 우려 및 정치적 이슈에 따른 부정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선업', '정부정책', '수주']</t>
+          <t>['솔리다임', '중복 상장', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14160</v>
+        <v>17320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.28%</t>
+          <t>'-5.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>194</v>
+        <v>289</v>
       </c>
       <c r="H11" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K11" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L11" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M11" t="n">
-        <v>14110</v>
+        <v>17280</v>
       </c>
       <c r="N11" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>21656352175</v>
+        <v>42589858380</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-106000</v>
+        <v>-285000</v>
       </c>
       <c r="S11" t="n">
-        <v>-57000</v>
+        <v>-201000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
+          <t>국가 경제 및 조선업 쇠퇴에 대한 부정적 전망. 삼성중공업 주가 하락에 대한 정부 및 시장 분위기 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['조선업', '정부정책', '수주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,169 +1476,169 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1209000</v>
+        <v>2550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.32%</t>
+          <t>'-5.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>581</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>1827</v>
+        <v>178</v>
       </c>
       <c r="H12" t="n">
-        <v>48.81</v>
+        <v>1.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1277000</v>
+        <v>2695</v>
       </c>
       <c r="K12" t="n">
-        <v>1265000</v>
+        <v>2645</v>
       </c>
       <c r="L12" t="n">
-        <v>1267000</v>
+        <v>2715</v>
       </c>
       <c r="M12" t="n">
-        <v>1183000</v>
+        <v>2510</v>
       </c>
       <c r="N12" t="n">
-        <v>48.82</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3234813156000</v>
+        <v>31029390645</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>2755</v>
       </c>
       <c r="Q12" t="n">
-        <v>465500</v>
+        <v>865</v>
       </c>
       <c r="R12" t="n">
-        <v>-293000</v>
+        <v>51000</v>
       </c>
       <c r="S12" t="n">
-        <v>-218000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>솔리다임 우회 상장 관련 소액주주 보호 청원 및 정치적 이슈로 인한 주가 하락 우려.</t>
+          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회 상장', '소액주주 보호']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18630</v>
+        <v>14105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-5.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.25</v>
+        <v>0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H13" t="n">
-        <v>3.07</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19710</v>
+        <v>14950</v>
       </c>
       <c r="K13" t="n">
-        <v>19450</v>
+        <v>14610</v>
       </c>
       <c r="L13" t="n">
-        <v>21850</v>
+        <v>14940</v>
       </c>
       <c r="M13" t="n">
-        <v>18460</v>
+        <v>14100</v>
       </c>
       <c r="N13" t="n">
-        <v>3.32</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>98476846635</v>
+        <v>22449348515</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>19000</v>
+        <v>-106000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-57000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>라온시큐어 보안주로서의 중요성 부각 및 주가 상승 기대. 2만원 안착 여부 및 외국인 매수세 주목.</t>
+          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안주', '정책', '외국인']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2535</v>
+        <v>18380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-6.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.34</v>
+        <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H14" t="n">
-        <v>1.14</v>
+        <v>3.07</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2695</v>
+        <v>19710</v>
       </c>
       <c r="K14" t="n">
-        <v>2645</v>
+        <v>19450</v>
       </c>
       <c r="L14" t="n">
-        <v>2715</v>
+        <v>21850</v>
       </c>
       <c r="M14" t="n">
-        <v>2510</v>
+        <v>18380</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8</v>
+        <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>30896710895</v>
+        <v>99736381515</v>
       </c>
       <c r="P14" t="n">
-        <v>2755</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>865</v>
+        <v>6320</v>
       </c>
       <c r="R14" t="n">
-        <v>51000</v>
+        <v>19000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
+          <t>보안주로서의 역할 및 외국인 매수세 유입에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['보안주', '외국인 매수', '주가 상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30750</v>
+        <v>30700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.43%</t>
+          <t>'-9.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>65431251775</v>
+        <v>66314187500</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.58%</t>
+          <t>'-10.98%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
         <v>352</v>
@@ -1892,13 +1892,13 @@
         <v>1895</v>
       </c>
       <c r="M16" t="n">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="N16" t="n">
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>72061436117</v>
+        <v>72325244777</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시 및 글로벌 강관 기술력 입증으로 인한 주가 상승 기대. 최근 3일간 코스피 수익률 3위 기록.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등 기대감. 국내외 다양한 글로벌 강관 기술력 입증.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재 공시', '강관 기술']</t>
+          <t>['스페이스X', '강관 기술력', '호재 공시']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8640</v>
+        <v>8650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.11%</t>
+          <t>'-11.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F17" t="n">
         <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17621996045</v>
+        <v>17660248125</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>테슬라 부품 공급 관련 언급. 주주환원 부재 및 과거 주가 흐름에 대한 부정적 시각 존재. 급락.</t>
+          <t>테슬라 부품 공급 관련 기대감과 함께 중복 상장 우려 및 주가 하락에 대한 논의.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['테슬라', '부품', '주주환원']</t>
+          <t>['테슬라', '부품 공급', '중복 상장']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7680</v>
+        <v>7750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-14.09%</t>
+          <t>'-13.31%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H18" t="n">
         <v>36.01</v>
@@ -2082,7 +2082,7 @@
         <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>20477596835</v>
+        <v>20639322400</v>
       </c>
       <c r="P18" t="n">
         <v>19150</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70100</v>
+        <v>70600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-14.51%</t>
+          <t>'-13.90%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F19" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G19" t="n">
-        <v>871</v>
+        <v>903</v>
       </c>
       <c r="H19" t="n">
         <v>9.380000000000001</v>
@@ -2174,7 +2174,7 @@
         <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>114862112850</v>
+        <v>117770156600</v>
       </c>
       <c r="P19" t="n">
         <v>184000</v>

--- a/data/trending_integrated_20261020_14.xlsx
+++ b/data/trending_integrated_20261020_14.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3290</v>
+        <v>73100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.86%</t>
+          <t>'+13.33%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>214</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>410</v>
+        <v>232</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>5.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2915</v>
+        <v>64500</v>
       </c>
       <c r="K2" t="n">
-        <v>2920</v>
+        <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>3445</v>
+        <v>79300</v>
       </c>
       <c r="M2" t="n">
-        <v>2875</v>
+        <v>66700</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>60925313431</v>
+        <v>147501221600</v>
       </c>
       <c r="P2" t="n">
-        <v>7050</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2500</v>
+        <v>17780</v>
       </c>
       <c r="R2" t="n">
-        <v>-831000</v>
+        <v>-17000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 사망설 루머에 따른 급등 가능성 및 지정학적 리스크 부각.</t>
+          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '지정학적 리스크', '급등 가능성']</t>
+          <t>['반도체', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,91 +643,91 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72700</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.71%</t>
+          <t>'+10.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
-        <v>226</v>
+        <v>507</v>
       </c>
       <c r="H3" t="n">
-        <v>5.95</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>64500</v>
+        <v>2915</v>
       </c>
       <c r="K3" t="n">
-        <v>68000</v>
+        <v>2920</v>
       </c>
       <c r="L3" t="n">
-        <v>79300</v>
+        <v>3445</v>
       </c>
       <c r="M3" t="n">
-        <v>66700</v>
+        <v>2875</v>
       </c>
       <c r="N3" t="n">
-        <v>5.66</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>145551797850</v>
+        <v>62955379027</v>
       </c>
       <c r="P3" t="n">
-        <v>148300</v>
+        <v>7050</v>
       </c>
       <c r="Q3" t="n">
-        <v>17780</v>
+        <v>2500</v>
       </c>
       <c r="R3" t="n">
-        <v>-17000</v>
+        <v>-831000</v>
       </c>
       <c r="S3" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>반도체 실적 개선 기대감 및 목표가 상향 리포트 언급, 주가 상승세.</t>
+          <t>김정은 사망설 등 북한 관련 루머 확산에 따른 주가 변동 가능성 언급. 소문 기반.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '실적', '목표가']</t>
+          <t>['김정은 사망설', '북한 루머', '주가 변동']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3980</v>
+        <v>9630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.13%</t>
+          <t>'+5.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>258</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>627</v>
       </c>
       <c r="H4" t="n">
-        <v>1.66</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3750</v>
+        <v>9120</v>
       </c>
       <c r="K4" t="n">
-        <v>3770</v>
+        <v>9500</v>
       </c>
       <c r="L4" t="n">
-        <v>4285</v>
+        <v>11250</v>
       </c>
       <c r="M4" t="n">
-        <v>3755</v>
+        <v>9370</v>
       </c>
       <c r="N4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>47543559896</v>
+        <v>251746669455</v>
       </c>
       <c r="P4" t="n">
-        <v>6660</v>
+        <v>11250</v>
       </c>
       <c r="Q4" t="n">
-        <v>2200</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>-138000</v>
+        <v>76000</v>
       </c>
       <c r="S4" t="n">
-        <v>-18000</v>
+        <v>22000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
+          <t>로봇, ESS, 이차전지 관련주로서 강한 상승세 및 조단위 시총 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['피하주사', '기술 계약', '시장 하락']</t>
+          <t>['로봇', 'ESS', '이차전지']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9470</v>
+        <v>3940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.84%</t>
+          <t>'+5.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>244</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>589</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9120</v>
+        <v>3750</v>
       </c>
       <c r="K5" t="n">
-        <v>9500</v>
+        <v>3770</v>
       </c>
       <c r="L5" t="n">
-        <v>11250</v>
+        <v>4285</v>
       </c>
       <c r="M5" t="n">
-        <v>9430</v>
+        <v>3755</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>245116695075</v>
+        <v>47944804916</v>
       </c>
       <c r="P5" t="n">
-        <v>11250</v>
+        <v>6660</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>2200</v>
       </c>
       <c r="R5" t="n">
-        <v>76000</v>
+        <v>-138000</v>
       </c>
       <c r="S5" t="n">
-        <v>22000</v>
+        <v>-18000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 관련주로서 강한 상승세 및 조단위 시총 기대감.</t>
+          <t>차세대 피하주사 기술 관련 계약 체결 소식 있으나, 시장 전반의 하락세 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '이차전지']</t>
+          <t>['피하주사', '기술 계약', '시장 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42850</v>
+        <v>16420</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>1173</v>
+        <v>279</v>
       </c>
       <c r="H6" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K6" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L6" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M6" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>14703535950</v>
+        <v>64844510105</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R6" t="n">
-        <v>25000</v>
+        <v>-69000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 임박 및 담관암 FDA 승인 가능성으로 인한 기대감. 주가 변동성에 대한 언급.</t>
+          <t>종목 부진 및 보호예수 물량에 대한 우려 표출. 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '담관암']</t>
+          <t>['보호예수', '종목 부진', '쓰레기 종목']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16100</v>
+        <v>43000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="G7" t="n">
-        <v>277</v>
+        <v>1188</v>
       </c>
       <c r="H7" t="n">
-        <v>2.03</v>
+        <v>13.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16200</v>
+        <v>42950</v>
       </c>
       <c r="K7" t="n">
-        <v>16500</v>
+        <v>42600</v>
       </c>
       <c r="L7" t="n">
-        <v>18620</v>
+        <v>43200</v>
       </c>
       <c r="M7" t="n">
-        <v>14650</v>
+        <v>41550</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07</v>
+        <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>62344373440</v>
+        <v>15090317475</v>
       </c>
       <c r="P7" t="n">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>14600</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>-69000</v>
+        <v>25000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>종목 부실 및 낮은 상승률에 대한 불만 표출과 보호예수 물량 부담 언급.</t>
+          <t>C1 발표 및 담관암 FDA 승인에 대한 기대감 표출. 클래스 1 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['부실 종목', '보호예수', '낮은 상승률']</t>
+          <t>['C1 발표', 'FDA 승인', '클래스 1']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7250</v>
+        <v>7260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>11263553950</v>
+        <v>11558595125</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209750</v>
+        <v>210250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G9" t="n">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2513024147750</v>
+        <v>2579637070250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적 언급 및 증시 하락에 대한 정부 정책 비판.</t>
+          <t>정치 관련 부정적 언급이 주를 이루며, 주가 하락에 대한 정부 정책 불신 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '정치적 이슈', '증시 하락']</t>
+          <t>['정치', '증시 하락', '정책 불신']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1214000</v>
+        <v>1220000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-4.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G10" t="n">
-        <v>1927</v>
+        <v>1818</v>
       </c>
       <c r="H10" t="n">
         <v>48.81</v>
@@ -1346,7 +1346,7 @@
         <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3297565591000</v>
+        <v>3359700279500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 중복 상장에 대한 우려 및 정치적 이슈에 따른 부정적 전망.</t>
+          <t>정치권 및 경영진 비판적 언급이 주를 이룸. 최태원 회장 발언 인용되나 부정적 뉘앙스.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복 상장', '정치적 이슈']</t>
+          <t>['정치권 비판', '솔리다임', '최태원 발언']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17320</v>
+        <v>17340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.36%</t>
+          <t>'-5.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
         <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>42589858380</v>
+        <v>43635820280</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2550</v>
+        <v>14150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.38%</t>
+          <t>'-5.35%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H12" t="n">
-        <v>1.14</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2695</v>
+        <v>14950</v>
       </c>
       <c r="K12" t="n">
-        <v>2645</v>
+        <v>14610</v>
       </c>
       <c r="L12" t="n">
-        <v>2715</v>
+        <v>14940</v>
       </c>
       <c r="M12" t="n">
-        <v>2510</v>
+        <v>14100</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>31029390645</v>
+        <v>23064341925</v>
       </c>
       <c r="P12" t="n">
-        <v>2755</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>51000</v>
+        <v>-106000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-57000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
+          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14105</v>
+        <v>2545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.65%</t>
+          <t>'-5.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H13" t="n">
-        <v>9.779999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14950</v>
+        <v>2695</v>
       </c>
       <c r="K13" t="n">
-        <v>14610</v>
+        <v>2645</v>
       </c>
       <c r="L13" t="n">
-        <v>14940</v>
+        <v>2715</v>
       </c>
       <c r="M13" t="n">
-        <v>14100</v>
+        <v>2510</v>
       </c>
       <c r="N13" t="n">
-        <v>9.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>22449348515</v>
+        <v>31130131365</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>2755</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>865</v>
       </c>
       <c r="R13" t="n">
-        <v>-106000</v>
+        <v>51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 및 주가 상승 기대감에도 불구하고, 공매도 관련 정치적 언급과 함께 부정적 심리가 혼재된 상황.</t>
+          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18380</v>
+        <v>18060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.75%</t>
+          <t>'-8.37%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="H14" t="n">
         <v>3.07</v>
@@ -1708,13 +1708,13 @@
         <v>21850</v>
       </c>
       <c r="M14" t="n">
-        <v>18380</v>
+        <v>18020</v>
       </c>
       <c r="N14" t="n">
         <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>99736381515</v>
+        <v>101579548795</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>보안주로서의 역할 및 외국인 매수세 유입에 따른 주가 상승 기대감.</t>
+          <t>주가 하락 및 개인 물량 넘김에 대한 의혹 제기. 보안주로서의 역할 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['보안주', '외국인 매수', '주가 상승']</t>
+          <t>['주가 하락', '개인 물량', '보안주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.57%</t>
+          <t>'-9.43%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
         <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>66314187500</v>
+        <v>67249912150</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.98%</t>
+          <t>'-10.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G16" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>72325244777</v>
+        <v>72461154250</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등 기대감. 국내외 다양한 글로벌 강관 기술력 입증.</t>
+          <t>스페이스X 관련 호재 공시로 상한가 기록, 글로벌 강관 기술력 입증. 2연상 기대감 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관 기술력', '호재 공시']</t>
+          <t>['스페이스X', '강관 기술', '호재 공시']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17660248125</v>
+        <v>17750425155</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7750</v>
+        <v>71000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.31%</t>
+          <t>'-13.41%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>267</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="G18" t="n">
-        <v>171</v>
+        <v>907</v>
       </c>
       <c r="H18" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K18" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L18" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M18" t="n">
-        <v>7600</v>
+        <v>70000</v>
       </c>
       <c r="N18" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O18" t="n">
-        <v>20639322400</v>
+        <v>120326223450</v>
       </c>
       <c r="P18" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R18" t="n">
-        <v>-86000</v>
+        <v>-628000</v>
       </c>
       <c r="S18" t="n">
-        <v>-48000</v>
+        <v>-70000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '정치', '급락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,91 +2115,91 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70600</v>
+        <v>7730</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.90%</t>
+          <t>'-13.53%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>263</v>
+        <v>89</v>
       </c>
       <c r="F19" t="n">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>903</v>
+        <v>176</v>
       </c>
       <c r="H19" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L19" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M19" t="n">
-        <v>70000</v>
+        <v>7600</v>
       </c>
       <c r="N19" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O19" t="n">
-        <v>117770156600</v>
+        <v>20804966905</v>
       </c>
       <c r="P19" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q19" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R19" t="n">
-        <v>-628000</v>
+        <v>-86000</v>
       </c>
       <c r="S19" t="n">
-        <v>-70000</v>
+        <v>-48000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '정치', '급락']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_14.xlsx
+++ b/data/trending_integrated_20261020_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73100</v>
+        <v>73400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+13.33%</t>
+          <t>'+13.80%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>147501221600</v>
+        <v>148800825250</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>3245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.46%</t>
+          <t>'+11.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>507</v>
+        <v>558</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>62955379027</v>
+        <v>64342849060</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 사망설 등 북한 관련 루머 확산에 따른 주가 변동 가능성 언급. 소문 기반.</t>
+          <t>김정은 사망설 루머 확산 및 유가 폭등 관련 언급. 빅텍 대장주로서의 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '북한 루머', '주가 변동']</t>
+          <t>['김정은', '사망설', '빅텍']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9630</v>
+        <v>9740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.59%</t>
+          <t>'+6.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.86</v>
       </c>
       <c r="E4" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="F4" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G4" t="n">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="H4" t="n">
         <v>0.88</v>
@@ -794,7 +794,7 @@
         <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>251746669455</v>
+        <v>257552748385</v>
       </c>
       <c r="P4" t="n">
         <v>11250</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 관련주로서 강한 상승세 및 조단위 시총 기대감.</t>
+          <t>로봇, ESS, 이차전지 관련 사업 엮임. 신고가 달성 및 조단위 시총 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '이차전지']</t>
+          <t>['로봇', 'ESS', '신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3940</v>
+        <v>3950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.07%</t>
+          <t>'+5.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
         <v>1.66</v>
@@ -886,7 +886,7 @@
         <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>47944804916</v>
+        <v>48255312940</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16420</v>
+        <v>43150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
-        <v>279</v>
+        <v>1209</v>
       </c>
       <c r="H6" t="n">
-        <v>2.03</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16200</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>16500</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>18620</v>
+        <v>43300</v>
       </c>
       <c r="M6" t="n">
-        <v>14650</v>
+        <v>41550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>64844510105</v>
+        <v>16018162825</v>
       </c>
       <c r="P6" t="n">
-        <v>62100</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>14600</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-69000</v>
+        <v>25000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>종목 부진 및 보호예수 물량에 대한 우려 표출. 타 종목과의 비교 언급.</t>
+          <t>C1 발표 및 담관암 FDA 승인에 대한 기대감 표출. 클래스 1 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보호예수', '종목 부진', '쓰레기 종목']</t>
+          <t>['C1 발표', 'FDA 승인', '클래스 1']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43000</v>
+        <v>16230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E7" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F7" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>1188</v>
+        <v>282</v>
       </c>
       <c r="H7" t="n">
-        <v>13.11</v>
+        <v>2.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42950</v>
+        <v>16200</v>
       </c>
       <c r="K7" t="n">
-        <v>42600</v>
+        <v>16500</v>
       </c>
       <c r="L7" t="n">
-        <v>43200</v>
+        <v>18620</v>
       </c>
       <c r="M7" t="n">
-        <v>41550</v>
+        <v>14650</v>
       </c>
       <c r="N7" t="n">
-        <v>13.04</v>
+        <v>1.07</v>
       </c>
       <c r="O7" t="n">
-        <v>15090317475</v>
+        <v>65585119110</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>62100</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>14600</v>
       </c>
       <c r="R7" t="n">
-        <v>25000</v>
+        <v>-69000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C1 발표 및 담관암 FDA 승인에 대한 기대감 표출. 클래스 1 가능성 언급.</t>
+          <t>종목 부진 및 보호예수 물량에 대한 우려 표출. 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '클래스 1']</t>
+          <t>['보호예수', '종목 부진', '쓰레기 종목']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7260</v>
+        <v>7280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>11558595125</v>
+        <v>11953361665</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210250</v>
+        <v>211250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="G9" t="n">
-        <v>1536</v>
+        <v>1490</v>
       </c>
       <c r="H9" t="n">
         <v>46.04</v>
@@ -1254,7 +1254,7 @@
         <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2579637070250</v>
+        <v>2667832585000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치 관련 부정적 언급이 주를 이루며, 주가 하락에 대한 정부 정책 불신 표출.</t>
+          <t>이재명 관련 정치적 논란 및 한국 증시 저평가 주장. 반도체 산업 성장성에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '증시 하락', '정책 불신']</t>
+          <t>['이재명', '정치', '저평가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1220000</v>
+        <v>1224000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.46%</t>
+          <t>'-4.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="G10" t="n">
-        <v>1818</v>
+        <v>1849</v>
       </c>
       <c r="H10" t="n">
         <v>48.81</v>
@@ -1346,7 +1346,7 @@
         <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>3359700279500</v>
+        <v>3455576336500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치권 및 경영진 비판적 언급이 주를 이룸. 최태원 회장 발언 인용되나 부정적 뉘앙스.</t>
+          <t>정치인 관련 부정적 언급 및 솔리다임 상장 관련 논란. 최태원 회장의 주가 전망 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치권 비판', '솔리다임', '최태원 발언']</t>
+          <t>['솔리다임', '최태원', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17340</v>
+        <v>17370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.25%</t>
+          <t>'-5.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F11" t="n">
         <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>43635820280</v>
+        <v>45610074805</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14150</v>
+        <v>14190</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.35%</t>
+          <t>'-5.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
         <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>9.779999999999999</v>
@@ -1530,7 +1530,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>23064341925</v>
+        <v>24111877365</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2545</v>
+        <v>2550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.57%</t>
+          <t>'-5.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H13" t="n">
         <v>1.14</v>
@@ -1622,7 +1622,7 @@
         <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>31130131365</v>
+        <v>31247393575</v>
       </c>
       <c r="P13" t="n">
         <v>2755</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18060</v>
+        <v>18480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.37%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.25</v>
       </c>
       <c r="E14" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H14" t="n">
         <v>3.07</v>
@@ -1714,7 +1714,7 @@
         <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>101579548795</v>
+        <v>103557253235</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 및 개인 물량 넘김에 대한 의혹 제기. 보안주로서의 역할 언급.</t>
+          <t>차트 분석 기반 부정적 전망. 개인 물량 넘기고 하한가 경고 언급. 로봇 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', '개인 물량', '보안주']</t>
+          <t>['차트', '개미', '보안']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30750</v>
+        <v>30800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.43%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="H15" t="n">
         <v>12.79</v>
@@ -1806,7 +1806,7 @@
         <v>12.81</v>
       </c>
       <c r="O15" t="n">
-        <v>67249912150</v>
+        <v>68568151925</v>
       </c>
       <c r="P15" t="n">
         <v>59300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.70%</t>
+          <t>'-10.64%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F16" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G16" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -1898,7 +1898,7 @@
         <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>72461154250</v>
+        <v>72659898371</v>
       </c>
       <c r="P16" t="n">
         <v>2970</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 상한가 기록, 글로벌 강관 기술력 입증. 2연상 기대감 존재.</t>
+          <t>스페이스X 관련 호재 공시 및 거래량 증가 확인. 2연상 기대감 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관 기술', '호재 공시']</t>
+          <t>['스페이스X', '호재 공시', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8650</v>
+        <v>8620</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.01%</t>
+          <t>'-11.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>17750425155</v>
+        <v>17885053435</v>
       </c>
       <c r="P17" t="n">
         <v>14940</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>테슬라 부품 공급 관련 기대감과 함께 중복 상장 우려 및 주가 하락에 대한 논의.</t>
+          <t>테슬라 부품 공급 관련 언급 및 주주환원 부족 지적. 공매도 관련 부정적 예측.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['테슬라', '부품 공급', '중복 상장']</t>
+          <t>['테슬라', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71000</v>
+        <v>7750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.41%</t>
+          <t>'-13.31%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>267</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>907</v>
+        <v>176</v>
       </c>
       <c r="H18" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L18" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M18" t="n">
-        <v>70000</v>
+        <v>7600</v>
       </c>
       <c r="N18" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O18" t="n">
-        <v>120326223450</v>
+        <v>20996105955</v>
       </c>
       <c r="P18" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q18" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R18" t="n">
-        <v>-628000</v>
+        <v>-86000</v>
       </c>
       <c r="S18" t="n">
-        <v>-70000</v>
+        <v>-48000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '정치', '급락']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,91 +2115,91 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7730</v>
+        <v>70800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-13.53%</t>
+          <t>'-13.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>89</v>
+        <v>269</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
-        <v>176</v>
+        <v>919</v>
       </c>
       <c r="H19" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K19" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L19" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M19" t="n">
-        <v>7600</v>
+        <v>70000</v>
       </c>
       <c r="N19" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O19" t="n">
-        <v>20804966905</v>
+        <v>123328501050</v>
       </c>
       <c r="P19" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q19" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R19" t="n">
-        <v>-86000</v>
+        <v>-628000</v>
       </c>
       <c r="S19" t="n">
-        <v>-48000</v>
+        <v>-70000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '정치', '급락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
